--- a/students.xlsx
+++ b/students.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="204">
   <si>
     <t>Name</t>
   </si>
@@ -601,6 +601,36 @@
   </si>
   <si>
     <t>K79T5R2Q</t>
+  </si>
+  <si>
+    <t>اسلام علاء عبدالعظيم</t>
+  </si>
+  <si>
+    <t>K39G5G1Q</t>
+  </si>
+  <si>
+    <t>يوسف ابراهيم عبدالعزيز</t>
+  </si>
+  <si>
+    <t>IsG4SJQh</t>
+  </si>
+  <si>
+    <t>بيتر نادي خلف</t>
+  </si>
+  <si>
+    <t>C39G5G1U</t>
+  </si>
+  <si>
+    <t>منار علاء</t>
+  </si>
+  <si>
+    <t>A3D7F6K8</t>
+  </si>
+  <si>
+    <t>رحمه هشام محمد</t>
+  </si>
+  <si>
+    <t>H9J2M4X7</t>
   </si>
 </sst>
 </file>
@@ -921,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultColWidth="18.125" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3640,6 +3670,76 @@
         <v>0</v>
       </c>
     </row>
+    <row r="96" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>0</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>0</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>0</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>0</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>0</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
